--- a/AAII_Financials/Quarterly/APO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/APO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="92">
   <si>
     <t>APO</t>
   </si>
@@ -656,344 +656,350 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="20" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="21" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>11065000</v>
+      </c>
+      <c r="E8" s="3">
         <v>4982000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>9792000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>9759000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>6754000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5488000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5216000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>7718000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5965000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>6989000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>10999000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2004000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>13671000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5270000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4353000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2348000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2143000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>889000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1264700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1074900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1382300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2294700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1296500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1018300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1508300</v>
       </c>
-      <c r="AB8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC8" s="3">
+      <c r="AC8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD8" s="3">
         <v>914800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>702700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>636600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>677800</v>
       </c>
-      <c r="AG8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH8" s="3">
+      <c r="AH8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI8" s="3">
         <v>517700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>690200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>166900</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>928300</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>711700</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>1131800</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>682100</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>685400</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>503700</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>7230000</v>
+      </c>
+      <c r="E9" s="3">
         <v>3160000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>6673000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>5669000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>4765000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2814000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3089000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>4102000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3593000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4057000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>7318000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1338000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>12101000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2301000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>126000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>112000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>108000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>98000</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V9" s="3" t="s">
         <v>5</v>
       </c>
@@ -1057,65 +1063,68 @@
       <c r="AP9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>3835000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1822000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3119000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4090000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1989000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2674000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2127000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3616000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2372000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2932000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3681000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>666000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1570000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2969000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4227000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2236000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2035000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>791000</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1179,8 +1188,11 @@
       <c r="AP10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1223,8 +1235,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1345,8 +1358,11 @@
       <c r="AP12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1467,53 +1483,56 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-39000</v>
+      </c>
+      <c r="E14" s="3">
         <v>419000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>113000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>89000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>189000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>433000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-507000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>713000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>36000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-163000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>581000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-923000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-63000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>377000</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
@@ -1589,53 +1608,56 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>414000</v>
+      </c>
+      <c r="E15" s="3">
         <v>397000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>391000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>400000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>332000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>308000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>296000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>281000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>260000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>238000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>217000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>241000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>180000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>165000</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R15" s="3" t="s">
         <v>5</v>
       </c>
@@ -1645,74 +1667,77 @@
       <c r="T15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U15" s="3">
+      <c r="U15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V15" s="3">
         <v>5500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>4800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>4300</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>3900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>6500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>1800</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>1600</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>2700</v>
-      </c>
-      <c r="AC15" s="3">
-        <v>2500</v>
       </c>
       <c r="AD15" s="3">
         <v>2500</v>
       </c>
       <c r="AE15" s="3">
-        <v>2300</v>
+        <v>2500</v>
       </c>
       <c r="AF15" s="3">
         <v>2300</v>
       </c>
       <c r="AG15" s="3">
+        <v>2300</v>
+      </c>
+      <c r="AH15" s="3">
         <v>2100</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>2200</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>4200</v>
-      </c>
-      <c r="AJ15" s="3">
-        <v>2100</v>
       </c>
       <c r="AK15" s="3">
         <v>2100</v>
       </c>
       <c r="AL15" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AM15" s="3">
         <v>5600</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>4400</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>2200</v>
       </c>
-      <c r="AO15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AP15" s="3">
+      <c r="AP15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ15" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1752,252 +1777,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>8636000</v>
+      </c>
+      <c r="E17" s="3">
         <v>4310000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>8017000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6839000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5737000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3867000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4106000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5033000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4516000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4964000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>8526000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2115000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>12843000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3168000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3065000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3778000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5718000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3164000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1696800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>648900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>746800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1021700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>672600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>531100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>702800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>-328400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>599400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>371400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>342500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>378000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>73900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>312700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>516300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>214900</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>392100</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>357500</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>610500</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>346000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>398400</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>282300</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2429000</v>
+      </c>
+      <c r="E18" s="3">
         <v>672000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1775000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2920000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1017000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1621000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1110000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2685000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1449000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2025000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2473000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-111000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>828000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2102000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1288000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1430000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-3575000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-2275000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-432100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>426000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>635500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1273000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>623900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>487200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>805500</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC18" s="3">
+      <c r="AC18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD18" s="3">
         <v>315400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>331300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>294100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>299800</v>
       </c>
-      <c r="AG18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH18" s="3">
+      <c r="AH18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI18" s="3">
         <v>205000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>173900</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-48000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>536200</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>354200</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>521300</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>336100</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>287000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>221400</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2040,252 +2072,259 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-30000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-36000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-33000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-13000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>218000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-87000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-70000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-24000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>26000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-34000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-22000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-48000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-32000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-7000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>549000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>653000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>772000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1339100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>427900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1064000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>448800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>604700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>278200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>333900</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC20" s="3">
+      <c r="AC20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD20" s="3">
         <v>108900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-42100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>65000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>35400</v>
       </c>
-      <c r="AG20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH20" s="3">
+      <c r="AH20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI20" s="3">
         <v>176800</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-112000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-52800</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>196100</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>96700</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>65100</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>58100</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>135500</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>42900</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2860000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1099000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2202000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3353000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1362000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1711000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1493000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3036000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1733000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2237000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2724000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>152000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1056000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2299000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1442000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-719000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-2784000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-1370000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>914400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>860800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1706500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1727800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1234400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>770000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1143500</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD21" s="3">
         <v>428700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>293200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>362800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>338900</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH21" s="3">
+      <c r="AH21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI21" s="3">
         <v>385400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>69500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>-96900</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>735500</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>457700</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>594800</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>398600</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>427100</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>269000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2328,27 +2367,27 @@
       <c r="P22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R22" s="3">
         <v>51000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>64000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>65000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>41000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>198800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>121000</v>
       </c>
-      <c r="W22" s="3">
-        <v>0</v>
-      </c>
       <c r="X22" s="3">
         <v>0</v>
       </c>
@@ -2406,252 +2445,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2485000</v>
+      </c>
+      <c r="E23" s="3">
         <v>283000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1752000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2899000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>845000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1181000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1724000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2086000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1438000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2187000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1961000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>883000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>951000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1791000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1230000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-945000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2987000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1544000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>708200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>732900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1699500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1721700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1228600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>765500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1139400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-2579700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>424400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>289200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>359100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>335200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-338500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>381800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>62000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-100800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>732300</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>450900</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>586400</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>394200</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>422500</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>264400</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>396000</v>
+      </c>
+      <c r="E24" s="3">
         <v>1694000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>592000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>438000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>243000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>62000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>317000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>261000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>422000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-1620000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>243000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>201000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>253000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>223000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-96000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-381000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-485000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>95600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>101400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>194100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>203200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>153100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>89400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>140300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-295900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>66400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-231900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>16900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>19700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>39400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>19100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>27500</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>8600</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>16700</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>16500</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>38400</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>39200</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>28200</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>29700</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2772,252 +2820,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2089000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1411000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1160000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2461000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>842000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>938000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1662000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1769000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1177000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1765000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3581000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>640000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>750000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1538000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1007000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-849000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2606000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1059000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>612500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>631400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1505500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1518500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1075500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>676100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>999100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-2283800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>358000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>521100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>342200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>315600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-377900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>362700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>34500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-109300</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>715600</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>434400</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>548000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>355000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>394300</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>234700</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-1947000</v>
+        <v>1289000</v>
       </c>
       <c r="E27" s="3">
+        <v>-1918000</v>
+      </c>
+      <c r="F27" s="3">
         <v>854000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1664000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>584000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>401000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1717000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>758000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>797000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1360000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2646000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>636000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>577000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>978000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>629000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-574000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1649000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-413000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>234400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>249200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>648600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>669700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>424900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>263200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>437200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-1005400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>156900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>354100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>155700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>139900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-196400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>158700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-4400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-62600</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>441900</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>192100</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>224000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>140600</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>161100</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>91400</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3138,8 +3195,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3224,17 +3284,17 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>5</v>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>5</v>
+      <c r="AG29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>0</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>5</v>
@@ -3242,12 +3302,12 @@
       <c r="AJ29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-254300</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3260,8 +3320,11 @@
       <c r="AP29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3382,8 +3445,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3504,252 +3570,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E32" s="3">
         <v>30000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>36000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>33000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>13000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-218000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>87000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>70000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>24000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-26000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>34000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>22000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>48000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>32000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>7000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-549000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-653000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-772000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1339100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-427900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1064000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-448800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-604700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-278200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-333900</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC32" s="3">
+      <c r="AC32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-108900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>42100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-65000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-35400</v>
       </c>
-      <c r="AG32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH32" s="3">
+      <c r="AH32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI32" s="3">
         <v>-176800</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>112000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>52800</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-196100</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-96700</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-65100</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-58100</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-135500</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-42900</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1361000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1906000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>684000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1736000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>630000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>442000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1486000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>811000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>853000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1427000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2756000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>682000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>599000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1010000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>629000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-574000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1649000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-413000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>234400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>249200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>648600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>669700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>424900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>263200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>437200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-1005400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>156900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>354100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>155700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>139900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-196400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>158700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-4400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-62600</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>187600</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>192100</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>224000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>140600</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>161100</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>91400</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3870,257 +3945,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1361000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1906000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>684000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1736000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>630000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>442000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1486000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>811000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>853000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1427000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2756000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>682000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>599000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1010000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>629000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-574000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1649000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-413000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>234400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>249200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>648600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>669700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>424900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>263200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>437200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-1005400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>156900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>354100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>155700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>139900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-196400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>158700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-4400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-62600</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>187600</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>192100</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>224000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>140600</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>161100</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>91400</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4163,8 +4247,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4207,175 +4292,179 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>26815000</v>
+      </c>
+      <c r="E41" s="3">
         <v>22570000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>19240000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>18415000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>13248000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>13300000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>16166000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>16660000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>16888000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>18139000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>15928000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>12935000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>12311000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>15876000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>9452000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>11515000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>13064000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>10562000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1380400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2762800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2630400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2725900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2448800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2644200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1611600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>647800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1601500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1284600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1012800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>767900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>659400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>907900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1152100</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1063100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>844200</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>985300</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>1125200</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>1152200</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>855000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>986400</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>20801000</v>
+      </c>
+      <c r="E42" s="3">
         <v>19376000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>19180000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>17556000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>14630000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>11717000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>12680000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>12227000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>12093000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>11673000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>10004000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>9218000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>8666000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>6525000</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -4451,130 +4540,136 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>11892000</v>
+      </c>
+      <c r="E43" s="3">
         <v>11165000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>10945000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>10840000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>10036000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>9424000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>8778000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>8026000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6667000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5624000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4603000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4566000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4739000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4693000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>465000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>430000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>408000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>367000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>489600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>519200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>425900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>434700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>462400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>487500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>485400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>644300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>415100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>440100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>449200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>381000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>378100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>335800</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>315200</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>328900</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>262600</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>287400</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>282500</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>249900</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>254900</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>297700</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4617,8 +4712,8 @@
       <c r="P44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4695,8 +4790,11 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4739,8 +4837,8 @@
       <c r="P45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
+      <c r="Q45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R45" s="3">
         <v>0</v>
@@ -4748,60 +4846,60 @@
       <c r="S45" s="3">
         <v>0</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U45" s="3">
+      <c r="T45" s="3">
+        <v>0</v>
+      </c>
+      <c r="U45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V45" s="3">
         <v>57800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>61300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>68200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>67500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>46600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>44200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>45700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>42900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>55200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>47800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>52400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>55700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>130100</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>167500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>173700</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>174100</v>
       </c>
-      <c r="AK45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AL45" s="3" t="s">
         <v>5</v>
       </c>
@@ -4817,53 +4915,56 @@
       <c r="AP45" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ45" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>61110000</v>
+      </c>
+      <c r="E46" s="3">
         <v>54289000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>50716000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>49597000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>39637000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>36654000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>38570000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>37880000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>36743000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>37013000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>32298000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>28211000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>28189000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>29303000</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4939,130 +5040,136 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>398319000</v>
+      </c>
+      <c r="E47" s="3">
         <v>379993000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>376614000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>366274000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>349305000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>329567000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>310872000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>303561000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>282459000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>271467000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>256337000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>232576000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>232403000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>220157000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>216789000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>205083000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>203944000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>221083000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>26121000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>22008900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>21597900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>22131700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>19171400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>13934700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>14203500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>13658600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>5425500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>5232900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>5138700</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>4835100</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>4301700</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>5016600</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>4423800</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>4818900</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>3291700</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>3077500</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>2626400</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>2566700</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>2408600</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>2337500</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -5105,8 +5212,8 @@
       <c r="P48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q48" s="3">
-        <v>0</v>
+      <c r="Q48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R48" s="3">
         <v>0</v>
@@ -5114,60 +5221,60 @@
       <c r="S48" s="3">
         <v>0</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U48" s="3">
+      <c r="T48" s="3">
+        <v>0</v>
+      </c>
+      <c r="U48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V48" s="3">
         <v>576700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>474200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>444800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>373300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>375100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>374500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>375600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>241200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>232700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>216700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>120600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>123600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>20000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>19300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>18300</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>18500</v>
       </c>
-      <c r="AK48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AL48" s="3" t="s">
         <v>5</v>
       </c>
@@ -5183,8 +5290,11 @@
       <c r="AP48" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ48" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -5192,121 +5302,124 @@
         <v>5912000</v>
       </c>
       <c r="E49" s="3">
+        <v>5912000</v>
+      </c>
+      <c r="F49" s="3">
         <v>5920000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5900000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4339000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4331000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4327000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4335000</v>
-      </c>
-      <c r="K49" s="3">
-        <v>4328000</v>
       </c>
       <c r="L49" s="3">
         <v>4328000</v>
       </c>
       <c r="M49" s="3">
+        <v>4328000</v>
+      </c>
+      <c r="N49" s="3">
         <v>4329000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4324000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4329000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4325000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>10905000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>10925000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>11020000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>10915000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>131800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>133400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>137500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>139600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>140500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>142100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>141200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>115200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>114500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>108800</v>
-      </c>
-      <c r="AE49" s="3">
-        <v>108200</v>
       </c>
       <c r="AF49" s="3">
         <v>108200</v>
       </c>
       <c r="AG49" s="3">
+        <v>108200</v>
+      </c>
+      <c r="AH49" s="3">
         <v>107800</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>107700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>106200</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>106700</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>107700</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>108000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>108600</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>109900</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>111600</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>113500</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5427,8 +5540,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5549,130 +5665,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>19428000</v>
+      </c>
+      <c r="E52" s="3">
         <v>18524000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>19065000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>19402000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>18288000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>16887000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>16953000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>15942000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>16275000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>14835000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>14545000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>12676000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>11897000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>11703000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1676000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1721000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1446000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1872000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1132000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1519700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1760000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1088700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>557000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>696500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>826100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>895400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>492900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>550700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>294700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>295100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>309600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>352000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>367900</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>384500</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>341500</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>595900</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>603400</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>566500</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>576900</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>601000</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5793,130 +5915,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>494048000</v>
+      </c>
+      <c r="E54" s="3">
         <v>467530000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>460949000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>449543000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>419550000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>395045000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>377895000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>368689000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>346504000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>334051000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>313488000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>283235000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>281984000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>270324000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>257217000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>250340000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>247850000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>261555000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>30501900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>28290600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>27541300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>27410100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>23669100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>18627900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>17958400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>16322800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>8542100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>8064300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>7348200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>6721500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>5991700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>6972200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>6639000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>6948500</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>6991100</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>6860400</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>6221900</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>6261600</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>5629600</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>5490200</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5959,8 +6087,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6003,175 +6132,179 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5689000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1874000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1384000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4330000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3051000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2881000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1893000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1101000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>910000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>849000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1627000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1940000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1688000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1676000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2975000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3032000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2937000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3208000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>145100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>209300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>581400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>650600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>728500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>855900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>831600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1439300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>595800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>603900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>491400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>475500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>496300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>494900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>486600</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>563000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>496900</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>722500</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>672900</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>671100</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>695600</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>777800</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>24074000</v>
+      </c>
+      <c r="E58" s="3">
         <v>20824000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>23885000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>19749000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>18520000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>15294000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>18945000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>15902000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>16785000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>13909000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>12293000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>10899000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>13879000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>13232000</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -6247,175 +6380,181 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1603000</v>
+      </c>
+      <c r="E59" s="3">
         <v>2401000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3262000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>833000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1569000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2275000</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J59" s="3">
+      <c r="J59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K59" s="3">
         <v>802000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1362000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2013000</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N59" s="3">
+      <c r="N59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O59" s="3">
         <v>672000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1167000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1606000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>227271000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>226775000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>224107000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>220654000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3302400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2829900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2101400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1768600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1257900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1224700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>965700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>614600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1032500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1067500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>813900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>690600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>525700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>844100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>770200</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>705400</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>814800</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>855500</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>679400</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>688900</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>602900</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>588200</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>31366000</v>
+      </c>
+      <c r="E60" s="3">
         <v>26826000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>30566000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>24970000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>23201000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>20505000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>22726000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>19671000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>20859000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>18474000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>15589000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>15228000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>18331000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>18027000</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6491,175 +6630,181 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>17810000</v>
+      </c>
+      <c r="E61" s="3">
         <v>19210000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>18404000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>17898000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>16247000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>13974000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>13355000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>13152000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>13936000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>14398000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>11820000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>10750000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>9942000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>10221000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>6522000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>10706000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>7908000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>13905000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>13687900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>13674100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>13730300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>14429700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>14287700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>11262400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>10779400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>9612900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>3500700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>3177300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>3210300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2749700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2215900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2241600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2237900</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>2387700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>2364500</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>2333700</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>2243200</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>2150900</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>2139000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>2194700</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>403390000</v>
+      </c>
+      <c r="E62" s="3">
         <v>381961000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>369464000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>366878000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>346241000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>328222000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>310834000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>304325000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>283295000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>274163000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>260834000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>239295000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>236384000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>224342000</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
@@ -6735,8 +6880,11 @@
       <c r="AP62" s="3">
         <v>0</v>
       </c>
+      <c r="AQ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6857,8 +7005,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6979,8 +7130,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7101,130 +7255,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>452566000</v>
+      </c>
+      <c r="E66" s="3">
         <v>427997000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>418434000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>409746000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>385689000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>362701000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>346915000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>337148000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>318090000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>307035000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>288243000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>265273000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>264657000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>252590000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>250577000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>251679000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>244171000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>250562000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>26712800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>25642700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>25176300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>25473000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>22239800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>17538300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>17029400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>15766200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>6689900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>6299700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>5969000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>5400000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>4615500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>5344700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>5089000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>5393600</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>5528100</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>5530900</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>4999900</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>5084200</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>4794400</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>4767100</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7267,8 +7427,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7389,8 +7550,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7511,8 +7675,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7547,11 +7714,11 @@
         <v>1398000</v>
       </c>
       <c r="N70" s="3">
+        <v>1398000</v>
+      </c>
+      <c r="O70" s="3">
         <v>1397000</v>
       </c>
-      <c r="O70" s="3">
-        <v>0</v>
-      </c>
       <c r="P70" s="3">
         <v>0</v>
       </c>
@@ -7568,7 +7735,7 @@
         <v>0</v>
       </c>
       <c r="U70" s="3">
-        <v>554200</v>
+        <v>0</v>
       </c>
       <c r="V70" s="3">
         <v>554200</v>
@@ -7616,7 +7783,7 @@
         <v>554200</v>
       </c>
       <c r="AK70" s="3">
-        <v>264400</v>
+        <v>554200</v>
       </c>
       <c r="AL70" s="3">
         <v>264400</v>
@@ -7625,16 +7792,19 @@
         <v>264400</v>
       </c>
       <c r="AN70" s="3">
+        <v>264400</v>
+      </c>
+      <c r="AO70" s="3">
         <v>264700</v>
       </c>
-      <c r="AO70" s="3">
-        <v>0</v>
-      </c>
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7755,130 +7925,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>6149000</v>
+      </c>
+      <c r="E72" s="3">
         <v>5157000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>7634000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7306000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>5919000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>5634000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>6022000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>4865000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>4376000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3862000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2972000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>535000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>153000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-172000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1007000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-2837000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1943000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-93000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1143900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1078900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>990800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>477300</v>
       </c>
-      <c r="Y72" s="3">
-        <v>0</v>
-      </c>
       <c r="Z72" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA72" s="3">
         <v>-396900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-653700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-1075300</v>
       </c>
-      <c r="AC72" s="3">
-        <v>0</v>
-      </c>
       <c r="AD72" s="3">
         <v>0</v>
       </c>
       <c r="AE72" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF72" s="3">
         <v>-222000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-372600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-473300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-273500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-430300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-481800</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-379500</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-560600</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>-755500</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>-838700</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>-986200</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>-1147800</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7999,8 +8175,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8121,8 +8300,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8243,130 +8425,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>19608000</v>
+      </c>
+      <c r="E76" s="3">
         <v>18553000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>21943000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>21739000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>17923000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>16578000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>15855000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>16465000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>13875000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>13389000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>12646000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7045000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8229000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8074000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>6640000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-1339000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3679000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>10993000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3234900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2093700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1810900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1383000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>875100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>535400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>374800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1298000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1210400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>825100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>767300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>822000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1073200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>995800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1000700</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>1198500</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>1065100</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>957700</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>912700</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>835100</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>723100</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8487,257 +8675,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1361000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1906000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>684000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1736000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>630000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>442000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1486000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>811000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>853000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1427000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2756000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>682000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>599000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1010000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>629000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-574000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1649000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-413000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>234400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>249200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>648600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>669700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>424900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>263200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>437200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-1005400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>156900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>354100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>155700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>139900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-196400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>158700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-4400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-62600</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>187600</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>192100</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>224000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>140600</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>161100</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>91400</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8780,130 +8977,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>332000</v>
+      </c>
+      <c r="E83" s="3">
         <v>308000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>296000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>281000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>260000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>238000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>217000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>241000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>180000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>165000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>153000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>149000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>121000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>106000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>161000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>162000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>138000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>133000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>7400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>6900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>7000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>6100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>5800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>4500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>4100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>4500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>4300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>4100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>3700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>3600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>4000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>3600</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>7600</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>3900</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>3100</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>6800</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>8400</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>4400</v>
-      </c>
-      <c r="AO83" s="3">
-        <v>4600</v>
       </c>
       <c r="AP83" s="3">
         <v>4600</v>
       </c>
+      <c r="AQ83" s="3">
+        <v>4600</v>
+      </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9024,8 +9225,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9146,8 +9350,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9268,8 +9475,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9390,8 +9600,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9512,130 +9725,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2881000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1620000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4669000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>303000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1262000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1012000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-4000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1854000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1333000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>70000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2064000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-364000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3551000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1071000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1465000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2344000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>3973000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-3993000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-1072900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1043800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1321900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-228800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-3131100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>577300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>69800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>867600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>247700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>384400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>158500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>292100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>43400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>375800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>395100</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>41500</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>189500</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>250400</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>420000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>223600</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>42100</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>271000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9678,8 +9897,9 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9722,8 +9942,8 @@
       <c r="P91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -9732,7 +9952,7 @@
         <v>0</v>
       </c>
       <c r="T91" s="3">
-        <v>-19500</v>
+        <v>0</v>
       </c>
       <c r="U91" s="3">
         <v>-19500</v>
@@ -9741,67 +9961,70 @@
         <v>-19500</v>
       </c>
       <c r="W91" s="3">
+        <v>-19500</v>
+      </c>
+      <c r="X91" s="3">
         <v>-7700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-5500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-11500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-10500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-19500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-18200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-20900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-9000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-4700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-4900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-4700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-4900</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-5100</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-2200</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-2600</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-2300</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-3600</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-2000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-1400</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9922,8 +10145,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10044,130 +10270,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-15537000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-8334000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-14218000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-13237000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-19629000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-16888000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-16250000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-14466000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-14700000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-16385000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-14688000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-10211000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-11868000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-5640000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-11273000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-11353000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3921000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>3103000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1208100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1115400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>753000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>18900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-830200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>767500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-15500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-759400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-11700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>146000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-23600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-374600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-77700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-393200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>223600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>97200</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-172800</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-225800</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-18400</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-12600</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-10400</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-50400</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10210,130 +10442,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>342000</v>
+      </c>
+      <c r="E96" s="3">
         <v>312000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>311000</v>
-      </c>
-      <c r="F96" s="3">
-        <v>306000</v>
       </c>
       <c r="G96" s="3">
         <v>306000</v>
       </c>
       <c r="H96" s="3">
+        <v>306000</v>
+      </c>
+      <c r="I96" s="3">
         <v>278000</v>
-      </c>
-      <c r="I96" s="3">
-        <v>277000</v>
       </c>
       <c r="J96" s="3">
         <v>277000</v>
       </c>
       <c r="K96" s="3">
+        <v>277000</v>
+      </c>
+      <c r="L96" s="3">
         <v>279000</v>
-      </c>
-      <c r="L96" s="3">
-        <v>259000</v>
       </c>
       <c r="M96" s="3">
         <v>259000</v>
       </c>
       <c r="N96" s="3">
-        <v>256000</v>
+        <v>259000</v>
       </c>
       <c r="O96" s="3">
         <v>256000</v>
       </c>
       <c r="P96" s="3">
+        <v>256000</v>
+      </c>
+      <c r="Q96" s="3">
         <v>241000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-240000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-264000</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-229000</v>
       </c>
       <c r="T96" s="3">
         <v>-229000</v>
       </c>
       <c r="U96" s="3">
+        <v>-229000</v>
+      </c>
+      <c r="V96" s="3">
         <v>-127600</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-125800</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-119500</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-144300</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-120800</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-116100</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-99800</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-212800</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-115800</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-104800</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-96300</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-118300</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-97100</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-90600</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-219200</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-138400</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-78000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-103900</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-184800</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-87100</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>172100</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-70800</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10454,8 +10690,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10576,8 +10815,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10698,187 +10940,193 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>17326000</v>
+      </c>
+      <c r="E100" s="3">
         <v>9872000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>8947000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>19164000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>17815000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>14274000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>15745000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>12251000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>11634000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>18342000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>15880000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>10221000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>5014000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>11523000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>7697000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>7733000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2040000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>11240000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>553800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-268100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1353100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1177000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>3766000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-375900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>342100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-432900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>80900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-256400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>124200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>191000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-214200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-227300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-310700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>80200</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-157700</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-164900</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-131000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>86500</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-150900</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-151600</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E101" s="3">
         <v>3000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-6000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>5000</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>-2000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>8000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-3000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>2000</v>
-      </c>
-      <c r="L101" s="3">
-        <v>3000</v>
       </c>
       <c r="M101" s="3">
         <v>3000</v>
       </c>
       <c r="N101" s="3">
+        <v>3000</v>
+      </c>
+      <c r="O101" s="3">
         <v>2000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-16000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>3000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>2000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-16000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-4000</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V101" s="3" t="s">
         <v>5</v>
       </c>
@@ -10891,8 +11139,8 @@
       <c r="Y101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
+      <c r="Z101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AA101" s="3">
         <v>0</v>
@@ -10942,126 +11190,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>4669000</v>
+      </c>
+      <c r="E102" s="3">
         <v>3157000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-610000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>6230000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-542000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1599000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-515000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-356000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1733000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2025000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>3264000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-357000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3301000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>6957000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2108000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1274000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>2076000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>10346000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1727300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-339800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>721800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>967100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-195300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>968900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>396300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-324700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>316900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>273900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>259100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>108500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-248500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-244600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>307900</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>218900</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-141400</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-140800</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>270600</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>297500</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-119300</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>69000</v>
       </c>
     </row>
